--- a/Examples/Example_2_the_basics/data_example2-2.xlsx
+++ b/Examples/Example_2_the_basics/data_example2-2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ufbabr-my.sharepoint.com/personal/daniel_diniz_ufba_br/Documents/Projetos/MT-PEU/Examples/Example_2_the_basics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ddssa\OneDrive - Universidade Federal da Bahia\Projetos\MT-PEU\Examples\Example_2_the_basics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62F565C6-45D7-40E6-8DEE-B7EB44D3D3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA32D94-181F-46C0-AFA4-E3330049888E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14303" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="independente" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="48">
   <si>
     <t>60.1</t>
   </si>
@@ -162,13 +162,16 @@
   </si>
   <si>
     <t>utemperature</t>
+  </si>
+  <si>
+    <t>0.01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -206,6 +209,10 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -474,577 +481,578 @@
       <c r="A2" s="1">
         <v>120</v>
       </c>
-      <c r="B2" s="1">
-        <v>1</v>
+      <c r="B2" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C2" s="1">
         <v>600</v>
       </c>
-      <c r="D2" s="1">
-        <v>1</v>
+      <c r="D2" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1">
         <v>60</v>
       </c>
-      <c r="B3" s="1">
-        <v>1</v>
+      <c r="B3" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C3" s="1">
         <v>600</v>
       </c>
-      <c r="D3" s="1">
-        <v>1</v>
+      <c r="D3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
         <v>60</v>
       </c>
-      <c r="B4" s="1">
-        <v>1</v>
+      <c r="B4" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C4" s="1">
         <v>612</v>
       </c>
-      <c r="D4" s="1">
-        <v>1</v>
+      <c r="D4" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1">
         <v>120</v>
       </c>
-      <c r="B5" s="1">
-        <v>1</v>
+      <c r="B5" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C5" s="1">
         <v>612</v>
       </c>
-      <c r="D5" s="1">
-        <v>1</v>
+      <c r="D5" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
         <v>120</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
+      <c r="B6" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C6" s="1">
         <v>612</v>
       </c>
-      <c r="D6" s="1">
-        <v>1</v>
+      <c r="D6" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1">
         <v>60</v>
       </c>
-      <c r="B7" s="1">
-        <v>1</v>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C7" s="2">
         <v>612</v>
       </c>
-      <c r="D7" s="1">
-        <v>1</v>
+      <c r="D7" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
         <v>60</v>
       </c>
-      <c r="B8" s="1">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C8" s="1">
         <v>620</v>
       </c>
-      <c r="D8" s="1">
-        <v>1</v>
+      <c r="D8" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
         <v>30</v>
       </c>
-      <c r="B9" s="1">
-        <v>1</v>
+      <c r="B9" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C9" s="1">
         <v>620</v>
       </c>
-      <c r="D9" s="1">
-        <v>1</v>
+      <c r="D9" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
         <v>15</v>
       </c>
-      <c r="B10" s="1">
-        <v>1</v>
+      <c r="B10" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C10" s="1">
         <v>620</v>
       </c>
-      <c r="D10" s="1">
-        <v>1</v>
+      <c r="D10" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
         <v>60</v>
       </c>
-      <c r="B11" s="1">
-        <v>1</v>
+      <c r="B11" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C11" s="1">
         <v>620</v>
       </c>
-      <c r="D11" s="1">
-        <v>1</v>
+      <c r="D11" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="1">
-        <v>1</v>
+      <c r="B12" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C12" s="1">
         <v>620</v>
       </c>
-      <c r="D12" s="1">
-        <v>1</v>
+      <c r="D12" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
         <v>90</v>
       </c>
-      <c r="B13" s="1">
-        <v>1</v>
+      <c r="B13" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C13" s="1">
         <v>620</v>
       </c>
-      <c r="D13" s="1">
-        <v>1</v>
+      <c r="D13" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
         <v>150</v>
       </c>
-      <c r="B14" s="1">
-        <v>1</v>
+      <c r="B14" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C14" s="1">
         <v>620</v>
       </c>
-      <c r="D14" s="1">
-        <v>1</v>
+      <c r="D14" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1">
         <v>60</v>
       </c>
-      <c r="B15" s="1">
-        <v>1</v>
+      <c r="B15" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C15" s="1">
         <v>620</v>
       </c>
-      <c r="D15" s="1">
-        <v>1</v>
+      <c r="D15" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
         <v>60</v>
       </c>
-      <c r="B16" s="1">
-        <v>1</v>
+      <c r="B16" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C16" s="1">
         <v>620</v>
       </c>
-      <c r="D16" s="1">
-        <v>1</v>
+      <c r="D16" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
         <v>60</v>
       </c>
-      <c r="B17" s="1">
-        <v>1</v>
+      <c r="B17" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C17" s="1">
         <v>620</v>
       </c>
-      <c r="D17" s="1">
-        <v>1</v>
+      <c r="D17" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
         <v>30</v>
       </c>
-      <c r="B18" s="1">
-        <v>1</v>
+      <c r="B18" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C18" s="1">
         <v>620</v>
       </c>
-      <c r="D18" s="1">
-        <v>1</v>
+      <c r="D18" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
         <v>90</v>
       </c>
-      <c r="B19" s="1">
-        <v>1</v>
+      <c r="B19" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C19" s="1">
         <v>620</v>
       </c>
-      <c r="D19" s="1">
-        <v>1</v>
+      <c r="D19" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
         <v>150</v>
       </c>
-      <c r="B20" s="1">
-        <v>1</v>
+      <c r="B20" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C20" s="1">
         <v>620</v>
       </c>
-      <c r="D20" s="1">
-        <v>1</v>
+      <c r="D20" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="1">
-        <v>1</v>
+      <c r="B21" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C21" s="1">
         <v>620</v>
       </c>
-      <c r="D21" s="1">
-        <v>1</v>
+      <c r="D21" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
         <v>120</v>
       </c>
-      <c r="B22" s="1">
-        <v>1</v>
+      <c r="B22" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C22" s="1">
         <v>620</v>
       </c>
-      <c r="D22" s="1">
-        <v>1</v>
+      <c r="D22" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
         <v>60</v>
       </c>
-      <c r="B23" s="1">
-        <v>1</v>
+      <c r="B23" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C23" s="1">
         <v>620</v>
       </c>
-      <c r="D23" s="1">
-        <v>1</v>
+      <c r="D23" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
         <v>60</v>
       </c>
-      <c r="B24" s="1">
-        <v>1</v>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C24" s="1">
         <v>620</v>
       </c>
-      <c r="D24" s="1">
-        <v>1</v>
+      <c r="D24" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
         <v>60</v>
       </c>
-      <c r="B25" s="1">
-        <v>1</v>
+      <c r="B25" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C25" s="1">
         <v>620</v>
       </c>
-      <c r="D25" s="1">
-        <v>1</v>
+      <c r="D25" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
         <v>60</v>
       </c>
-      <c r="B26" s="1">
-        <v>1</v>
+      <c r="B26" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C26" s="1">
         <v>620</v>
       </c>
-      <c r="D26" s="1">
-        <v>1</v>
+      <c r="D26" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
         <v>60</v>
       </c>
-      <c r="B27" s="1">
-        <v>1</v>
+      <c r="B27" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C27" s="1">
         <v>620</v>
       </c>
-      <c r="D27" s="1">
-        <v>1</v>
+      <c r="D27" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
         <v>60</v>
       </c>
-      <c r="B28" s="1">
-        <v>1</v>
+      <c r="B28" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C28" s="1">
         <v>620</v>
       </c>
-      <c r="D28" s="1">
-        <v>1</v>
+      <c r="D28" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
         <v>30</v>
       </c>
-      <c r="B29" s="1">
-        <v>1</v>
+      <c r="B29" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C29" s="1">
         <v>631</v>
       </c>
-      <c r="D29" s="1">
-        <v>1</v>
+      <c r="D29" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="1">
-        <v>1</v>
+      <c r="B30" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C30" s="1">
         <v>631</v>
       </c>
-      <c r="D30" s="1">
-        <v>1</v>
+      <c r="D30" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="1">
-        <v>1</v>
+      <c r="B31" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C31" s="1">
         <v>631</v>
       </c>
-      <c r="D31" s="1">
-        <v>1</v>
+      <c r="D31" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
         <v>30</v>
       </c>
-      <c r="B32" s="1">
-        <v>1</v>
+      <c r="B32" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C32" s="1">
         <v>631</v>
       </c>
-      <c r="D32" s="1">
-        <v>1</v>
+      <c r="D32" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
         <v>45</v>
       </c>
-      <c r="B33" s="1">
-        <v>1</v>
+      <c r="B33" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C33" s="1">
         <v>631</v>
       </c>
-      <c r="D33" s="1">
-        <v>1</v>
+      <c r="D33" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
         <v>15</v>
       </c>
-      <c r="B34" s="1">
-        <v>1</v>
+      <c r="B34" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C34" s="1">
         <v>639</v>
       </c>
-      <c r="D34" s="1">
-        <v>1</v>
+      <c r="D34" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
         <v>30</v>
       </c>
-      <c r="B35" s="1">
-        <v>1</v>
+      <c r="B35" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C35" s="1">
         <v>639</v>
       </c>
-      <c r="D35" s="1">
-        <v>1</v>
+      <c r="D35" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
         <v>90</v>
       </c>
-      <c r="B36" s="1">
-        <v>1</v>
+      <c r="B36" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C36" s="1">
         <v>639</v>
       </c>
-      <c r="D36" s="1">
-        <v>1</v>
+      <c r="D36" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
         <v>25</v>
       </c>
-      <c r="B37" s="1">
-        <v>1</v>
+      <c r="B37" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C37" s="1">
         <v>639</v>
       </c>
-      <c r="D37" s="1">
-        <v>1</v>
+      <c r="D37" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="1">
-        <v>1</v>
+      <c r="B38" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C38" s="1">
         <v>639</v>
       </c>
-      <c r="D38" s="1">
-        <v>1</v>
+      <c r="D38" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
         <v>60</v>
       </c>
-      <c r="B39" s="1">
-        <v>1</v>
+      <c r="B39" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C39" s="1">
         <v>639</v>
       </c>
-      <c r="D39" s="1">
-        <v>1</v>
+      <c r="D39" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
         <v>30</v>
       </c>
-      <c r="B40" s="1">
-        <v>1</v>
+      <c r="B40" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C40" s="1">
         <v>639</v>
       </c>
-      <c r="D40" s="1">
-        <v>1</v>
+      <c r="D40" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
         <v>30</v>
       </c>
-      <c r="B41" s="1">
-        <v>1</v>
+      <c r="B41" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C41" s="1">
         <v>639</v>
       </c>
-      <c r="D41" s="1">
-        <v>1</v>
+      <c r="D41" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
         <v>60</v>
       </c>
-      <c r="B42" s="1">
-        <v>1</v>
+      <c r="B42" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C42" s="1">
         <v>639</v>
       </c>
-      <c r="D42" s="1">
-        <v>1</v>
+      <c r="D42" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
